--- a/research/traditional_assets/database/data/greece/greece_real_estate_development.xlsx
+++ b/research/traditional_assets/database/data/greece/greece_real_estate_development.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0968</v>
+        <v>-0.0513</v>
       </c>
       <c r="G2">
-        <v>-53.72727272727273</v>
+        <v>-58.18181818181819</v>
       </c>
       <c r="H2">
-        <v>-53.72727272727273</v>
+        <v>-58.18181818181819</v>
       </c>
       <c r="I2">
-        <v>-58.63636363636364</v>
+        <v>-54.54545454545455</v>
       </c>
       <c r="J2">
-        <v>-58.63636363636364</v>
+        <v>-54.54545454545455</v>
       </c>
       <c r="K2">
-        <v>-0.128</v>
+        <v>-0.9320000000000001</v>
       </c>
       <c r="L2">
-        <v>-11.63636363636364</v>
+        <v>-84.72727272727273</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.31</v>
+        <v>0.425</v>
       </c>
       <c r="V2">
-        <v>0.03141486810551559</v>
+        <v>0.02114427860696517</v>
       </c>
       <c r="W2">
-        <v>-0.03478260869565217</v>
+        <v>-0.2512129380053909</v>
       </c>
       <c r="X2">
-        <v>0.05830223824767124</v>
+        <v>0.1125970714034857</v>
       </c>
       <c r="Y2">
-        <v>-0.09308484694332342</v>
+        <v>-0.3638100094088765</v>
       </c>
       <c r="Z2">
-        <v>0.001502321770008194</v>
+        <v>0.00133495145631068</v>
       </c>
       <c r="AA2">
-        <v>-0.08809068560502595</v>
+        <v>-0.07281553398058252</v>
       </c>
       <c r="AB2">
-        <v>0.05661036635433889</v>
+        <v>0.1053489368097117</v>
       </c>
       <c r="AC2">
-        <v>-0.1447010519593648</v>
+        <v>-0.1781644707902942</v>
       </c>
       <c r="AD2">
-        <v>5.84</v>
+        <v>5.18</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>5.84</v>
+        <v>5.18</v>
       </c>
       <c r="AG2">
-        <v>4.529999999999999</v>
+        <v>4.755</v>
       </c>
       <c r="AH2">
-        <v>0.1228439209087084</v>
+        <v>0.2049050632911392</v>
       </c>
       <c r="AI2">
-        <v>0.6115183246073298</v>
+        <v>0.6870026525198939</v>
       </c>
       <c r="AJ2">
-        <v>0.0979883192731992</v>
+        <v>0.1913095956547978</v>
       </c>
       <c r="AK2">
-        <v>0.5497572815533981</v>
+        <v>0.668306394940267</v>
       </c>
       <c r="AL2">
-        <v>0.256</v>
+        <v>0.296</v>
       </c>
       <c r="AM2">
-        <v>0.255</v>
+        <v>0.296</v>
       </c>
       <c r="AN2">
-        <v>-9.139280125195619</v>
+        <v>-8.705882352941176</v>
       </c>
       <c r="AO2">
-        <v>-2.51953125</v>
+        <v>-2.027027027027027</v>
       </c>
       <c r="AP2">
-        <v>-7.089201877934271</v>
+        <v>-7.991596638655462</v>
       </c>
       <c r="AQ2">
-        <v>-2.529411764705882</v>
+        <v>-2.027027027027027</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0968</v>
+        <v>-0.0513</v>
       </c>
       <c r="G3">
-        <v>-53.72727272727273</v>
+        <v>-58.18181818181819</v>
       </c>
       <c r="H3">
-        <v>-53.72727272727273</v>
+        <v>-58.18181818181819</v>
       </c>
       <c r="I3">
-        <v>-58.63636363636364</v>
+        <v>-54.54545454545455</v>
       </c>
       <c r="J3">
-        <v>-58.63636363636364</v>
+        <v>-54.54545454545455</v>
       </c>
       <c r="K3">
-        <v>-0.128</v>
+        <v>-0.9320000000000001</v>
       </c>
       <c r="L3">
-        <v>-11.63636363636364</v>
+        <v>-84.72727272727273</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.31</v>
+        <v>0.425</v>
       </c>
       <c r="V3">
-        <v>0.03141486810551559</v>
+        <v>0.02114427860696517</v>
       </c>
       <c r="W3">
-        <v>-0.03478260869565217</v>
+        <v>-0.2512129380053909</v>
       </c>
       <c r="X3">
-        <v>0.05830223824767124</v>
+        <v>0.1125970714034857</v>
       </c>
       <c r="Y3">
-        <v>-0.09308484694332342</v>
+        <v>-0.3638100094088765</v>
       </c>
       <c r="Z3">
-        <v>0.001502321770008194</v>
+        <v>0.00133495145631068</v>
       </c>
       <c r="AA3">
-        <v>-0.08809068560502595</v>
+        <v>-0.07281553398058252</v>
       </c>
       <c r="AB3">
-        <v>0.05661036635433889</v>
+        <v>0.1053489368097117</v>
       </c>
       <c r="AC3">
-        <v>-0.1447010519593648</v>
+        <v>-0.1781644707902942</v>
       </c>
       <c r="AD3">
-        <v>5.84</v>
+        <v>5.18</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>5.84</v>
+        <v>5.18</v>
       </c>
       <c r="AG3">
-        <v>4.529999999999999</v>
+        <v>4.755</v>
       </c>
       <c r="AH3">
-        <v>0.1228439209087084</v>
+        <v>0.2049050632911392</v>
       </c>
       <c r="AI3">
-        <v>0.6115183246073298</v>
+        <v>0.6870026525198939</v>
       </c>
       <c r="AJ3">
-        <v>0.0979883192731992</v>
+        <v>0.1913095956547978</v>
       </c>
       <c r="AK3">
-        <v>0.5497572815533981</v>
+        <v>0.668306394940267</v>
       </c>
       <c r="AL3">
-        <v>0.256</v>
+        <v>0.296</v>
       </c>
       <c r="AM3">
-        <v>0.255</v>
+        <v>0.296</v>
       </c>
       <c r="AN3">
-        <v>-9.139280125195619</v>
+        <v>-8.705882352941176</v>
       </c>
       <c r="AO3">
-        <v>-2.51953125</v>
+        <v>-2.027027027027027</v>
       </c>
       <c r="AP3">
-        <v>-7.089201877934271</v>
+        <v>-7.991596638655462</v>
       </c>
       <c r="AQ3">
-        <v>-2.529411764705882</v>
+        <v>-2.027027027027027</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/greece/greece_real_estate_development.xlsx
+++ b/research/traditional_assets/database/data/greece/greece_real_estate_development.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,34 +588,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0513</v>
+        <v>0.0372</v>
       </c>
       <c r="G2">
-        <v>-58.18181818181819</v>
+        <v>-0.3760893476605466</v>
       </c>
       <c r="H2">
-        <v>-58.18181818181819</v>
+        <v>-0.3760893476605466</v>
       </c>
       <c r="I2">
-        <v>-54.54545454545455</v>
+        <v>-0.3450376512395296</v>
       </c>
       <c r="J2">
-        <v>-54.54545454545455</v>
+        <v>-0.2275605461746421</v>
       </c>
       <c r="K2">
-        <v>-0.9320000000000001</v>
+        <v>12.584</v>
       </c>
       <c r="L2">
-        <v>-84.72727272727273</v>
+        <v>1.064726288180049</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.008352578906851423</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0.1724411951684679</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +624,82 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>2.17</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>0.425</v>
+        <v>24.632</v>
       </c>
       <c r="V2">
-        <v>0.02114427860696517</v>
+        <v>0.09481139337952271</v>
       </c>
       <c r="W2">
-        <v>-0.2512129380053909</v>
+        <v>2.549821860947769</v>
       </c>
       <c r="X2">
-        <v>0.1125970714034857</v>
+        <v>0.08174306237621508</v>
       </c>
       <c r="Y2">
-        <v>-0.3638100094088765</v>
+        <v>2.468078798571554</v>
       </c>
       <c r="Z2">
-        <v>0.00133495145631068</v>
+        <v>0.09494316584327429</v>
       </c>
       <c r="AA2">
-        <v>-0.07281553398058252</v>
+        <v>-0.03351785709973364</v>
       </c>
       <c r="AB2">
-        <v>0.1053489368097117</v>
+        <v>0.0775272981495571</v>
       </c>
       <c r="AC2">
-        <v>-0.1781644707902942</v>
+        <v>-0.1110451552492907</v>
       </c>
       <c r="AD2">
-        <v>5.18</v>
+        <v>69.19</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>5.18</v>
+        <v>69.19</v>
       </c>
       <c r="AG2">
-        <v>4.755</v>
+        <v>44.55799999999999</v>
       </c>
       <c r="AH2">
-        <v>0.2049050632911392</v>
+        <v>0.2103103437794462</v>
       </c>
       <c r="AI2">
-        <v>0.6870026525198939</v>
+        <v>0.3083470742902981</v>
       </c>
       <c r="AJ2">
-        <v>0.1913095956547978</v>
+        <v>0.1463999632012301</v>
       </c>
       <c r="AK2">
-        <v>0.668306394940267</v>
+        <v>0.2230599024820032</v>
       </c>
       <c r="AL2">
-        <v>0.296</v>
+        <v>1.333</v>
       </c>
       <c r="AM2">
-        <v>0.296</v>
+        <v>1.248</v>
       </c>
       <c r="AN2">
-        <v>-8.705882352941176</v>
+        <v>-17.38005526249686</v>
       </c>
       <c r="AO2">
-        <v>-2.027027027027027</v>
+        <v>-3.059264816204051</v>
       </c>
       <c r="AP2">
-        <v>-7.991596638655462</v>
+        <v>-11.19266515950766</v>
       </c>
       <c r="AQ2">
-        <v>-2.027027027027027</v>
+        <v>-3.267628205128205</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kekrops S.A. (ATSE:KEKR)</t>
+          <t>Dimand S.A. (ATSE:DIMAND)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -715,35 +718,32 @@
           <t>Real Estate (Development)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.0513</v>
-      </c>
       <c r="G3">
-        <v>-58.18181818181819</v>
+        <v>-0.3347457627118644</v>
       </c>
       <c r="H3">
-        <v>-58.18181818181819</v>
+        <v>-0.3347457627118644</v>
       </c>
       <c r="I3">
-        <v>-54.54545454545455</v>
+        <v>-0.3076271186440678</v>
       </c>
       <c r="J3">
-        <v>-54.54545454545455</v>
+        <v>-0.1538135593220339</v>
       </c>
       <c r="K3">
-        <v>-0.9320000000000001</v>
+        <v>0.584</v>
       </c>
       <c r="L3">
-        <v>-84.72727272727273</v>
+        <v>0.04949152542372881</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>2.17</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.009986194201564656</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.715753424657534</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +752,210 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>2.17</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>0.425</v>
+        <v>24.5</v>
       </c>
       <c r="V3">
-        <v>0.02114427860696517</v>
+        <v>0.1127473538886332</v>
       </c>
       <c r="W3">
-        <v>-0.2512129380053909</v>
+        <v>0.01489795918367347</v>
       </c>
       <c r="X3">
-        <v>0.1125970714034857</v>
+        <v>0.08401702513586842</v>
       </c>
       <c r="Y3">
-        <v>-0.3638100094088765</v>
+        <v>-0.06911906595219496</v>
       </c>
       <c r="Z3">
-        <v>0.00133495145631068</v>
+        <v>0.100536764079407</v>
       </c>
       <c r="AA3">
-        <v>-0.07281553398058252</v>
+        <v>-0.01546391752577319</v>
       </c>
       <c r="AB3">
-        <v>0.1053489368097117</v>
+        <v>0.07777327837769725</v>
       </c>
       <c r="AC3">
-        <v>-0.1781644707902942</v>
+        <v>-0.09323719590347045</v>
       </c>
       <c r="AD3">
-        <v>5.18</v>
+        <v>63.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>5.18</v>
+        <v>63.5</v>
       </c>
       <c r="AG3">
-        <v>4.755</v>
+        <v>39</v>
       </c>
       <c r="AH3">
-        <v>0.2049050632911392</v>
+        <v>0.2261396011396011</v>
       </c>
       <c r="AI3">
-        <v>0.6870026525198939</v>
+        <v>0.3114271701814615</v>
       </c>
       <c r="AJ3">
-        <v>0.1913095956547978</v>
+        <v>0.1521654311353882</v>
       </c>
       <c r="AK3">
-        <v>0.668306394940267</v>
+        <v>0.2173913043478261</v>
       </c>
       <c r="AL3">
-        <v>0.296</v>
+        <v>1.05</v>
       </c>
       <c r="AM3">
-        <v>0.296</v>
+        <v>0.9750000000000001</v>
       </c>
       <c r="AN3">
-        <v>-8.705882352941176</v>
+        <v>-17.93785310734463</v>
       </c>
       <c r="AO3">
-        <v>-2.027027027027027</v>
+        <v>-3.457142857142857</v>
       </c>
       <c r="AP3">
-        <v>-7.991596638655462</v>
+        <v>-11.01694915254237</v>
       </c>
       <c r="AQ3">
-        <v>-2.027027027027027</v>
+        <v>-3.723076923076923</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kekrops S.A. (ATSE:KEKR)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Real Estate (Development)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.0372</v>
+      </c>
+      <c r="G4">
+        <v>-26.05263157894737</v>
+      </c>
+      <c r="H4">
+        <v>-26.05263157894737</v>
+      </c>
+      <c r="I4">
+        <v>-23.57894736842105</v>
+      </c>
+      <c r="J4">
+        <v>-19.31228070175439</v>
+      </c>
+      <c r="K4">
+        <v>12</v>
+      </c>
+      <c r="L4">
+        <v>631.578947368421</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>-0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>-0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0.132</v>
+      </c>
+      <c r="V4">
+        <v>0.003105882352941177</v>
+      </c>
+      <c r="W4">
+        <v>5.084745762711865</v>
+      </c>
+      <c r="X4">
+        <v>0.07946909961656173</v>
+      </c>
+      <c r="Y4">
+        <v>5.005276663095303</v>
+      </c>
+      <c r="Z4">
+        <v>0.002670414617006325</v>
+      </c>
+      <c r="AA4">
+        <v>-0.05157179667369408</v>
+      </c>
+      <c r="AB4">
+        <v>0.07728131792141694</v>
+      </c>
+      <c r="AC4">
+        <v>-0.128853114595111</v>
+      </c>
+      <c r="AD4">
+        <v>5.69</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>5.69</v>
+      </c>
+      <c r="AG4">
+        <v>5.558000000000001</v>
+      </c>
+      <c r="AH4">
+        <v>0.1180742892716331</v>
+      </c>
+      <c r="AI4">
+        <v>0.2776964372864812</v>
+      </c>
+      <c r="AJ4">
+        <v>0.1156519205959466</v>
+      </c>
+      <c r="AK4">
+        <v>0.2730130661165144</v>
+      </c>
+      <c r="AL4">
+        <v>0.283</v>
+      </c>
+      <c r="AM4">
+        <v>0.273</v>
+      </c>
+      <c r="AN4">
+        <v>-12.90249433106576</v>
+      </c>
+      <c r="AO4">
+        <v>-1.583038869257951</v>
+      </c>
+      <c r="AP4">
+        <v>-12.6031746031746</v>
+      </c>
+      <c r="AQ4">
+        <v>-1.641025641025641</v>
       </c>
     </row>
   </sheetData>
